--- a/examples/schedule_demo.xlsx
+++ b/examples/schedule_demo.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>06.07 - 12.07</t>
+          <t>20.07 - 26.07</t>
         </is>
       </c>
     </row>
